--- a/SGI_Sistema-de-gestao-integrado/SGA_Sistema-de-gestao-ambiental/Registos_SGA_Plasticom/SGA-19_ESG_Ambiental_GEE.xlsx
+++ b/SGI_Sistema-de-gestao-integrado/SGA_Sistema-de-gestao-ambiental/Registos_SGA_Plasticom/SGA-19_ESG_Ambiental_GEE.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Project Portfolios\manufacturing-performance-analytics\SGI_Sistema-de-gestao-integrado\SGA_Sistema-de-gestao-ambiental\Registos_SGA_Plasticom\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FA5EAF3B-5FEA-4DFB-82A9-CC30CC6647C2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{26A002B7-02FE-4406-9E9E-BABBA67ABC8A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1920" yWindow="1920" windowWidth="17280" windowHeight="8880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -4676,7 +4676,7 @@
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-C694-4EFC-BC22-013AA7EEDE7C}"/>
+              <c16:uniqueId val="{00000000-CAD7-4838-9359-B57C3B7B7C54}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -4833,7 +4833,7 @@
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-A04E-410B-93B0-9AA6DA882BAB}"/>
+              <c16:uniqueId val="{00000000-C6C8-427C-B3BF-0E1C7C9C952D}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -4900,7 +4900,7 @@
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000001-A04E-410B-93B0-9AA6DA882BAB}"/>
+              <c16:uniqueId val="{00000001-C6C8-427C-B3BF-0E1C7C9C952D}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
